--- a/data/trans_dic/P55$amigo-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P55$amigo-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,96</t>
+          <t>0,0; 38,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,82</t>
+          <t>0,0; 57,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,69</t>
+          <t>0,0; 24,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,51</t>
+          <t>0,0; 36,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,14; 28,4</t>
+          <t>3,12; 29,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,58</t>
+          <t>0,0; 25,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,26</t>
+          <t>0,0; 39,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 19,26</t>
+          <t>2,03; 19,23</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,91</t>
+          <t>0,0; 26,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,85</t>
+          <t>0,0; 75,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,88</t>
+          <t>0,0; 72,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,74</t>
+          <t>0,0; 24,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,29</t>
+          <t>0,0; 29,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,77</t>
+          <t>0,0; 30,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 15,52</t>
+          <t>1,52; 14,77</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,14</t>
+          <t>0,0; 41,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,62</t>
+          <t>0,0; 13,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,27</t>
+          <t>0,0; 28,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,6</t>
+          <t>0,0; 15,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,81</t>
+          <t>0,0; 24,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 9,62</t>
+          <t>1,13; 9,7</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,12</t>
+          <t>0,0; 7,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,56</t>
+          <t>0,0; 8,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 10,76</t>
+          <t>1,81; 11,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,71</t>
+          <t>0,0; 24,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,84</t>
+          <t>0,0; 19,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,58</t>
+          <t>0,0; 9,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,05</t>
+          <t>0,0; 7,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,91</t>
+          <t>0,0; 5,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,46</t>
+          <t>0,0; 9,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,75</t>
+          <t>1,85; 8,79</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,76</t>
+          <t>0,0; 9,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 13,63</t>
+          <t>1,32; 14,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,78</t>
+          <t>0,0; 7,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,62</t>
+          <t>0,0; 11,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,06; 8,25</t>
+          <t>2,25; 8,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,28</t>
+          <t>0,0; 6,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,5</t>
+          <t>0,0; 6,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 8,1</t>
+          <t>2,47; 8,15</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 76,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,13</t>
+          <t>0,51; 5,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,63</t>
+          <t>0,79; 6,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,36</t>
+          <t>1,95; 7,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,83</t>
+          <t>0,5; 5,02</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,63</t>
+          <t>0,79; 6,65</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,26; 8,14</t>
+          <t>2,01; 7,53</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,81</t>
+          <t>0,0; 5,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 10,12</t>
+          <t>0,71; 9,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,7</t>
+          <t>0,0; 5,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 8,13</t>
+          <t>2,66; 8,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,04</t>
+          <t>0,89; 5,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,09</t>
+          <t>0,35; 3,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,81</t>
+          <t>0,92; 5,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,77</t>
+          <t>2,92; 6,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,18</t>
+          <t>1,0; 3,87</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,08</t>
+          <t>0,75; 4,03</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,26</t>
+          <t>0,86; 4,15</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,36</t>
+          <t>3,46; 6,46</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3952</t>
+          <t>0; 3883</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4773</t>
+          <t>0; 4812</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1634</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2482</t>
+          <t>0; 2921</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4881</t>
+          <t>0; 4828</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1448</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2125</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>435; 3935</t>
+          <t>432; 4134</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5543</t>
+          <t>0; 5895</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4928</t>
+          <t>0; 4656</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 2033</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>526; 4979</t>
+          <t>525; 4973</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1844</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1973</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1560</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4349</t>
+          <t>0; 4621</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4060</t>
+          <t>0; 4064</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1828</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4488</t>
+          <t>0; 4841</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3531</t>
+          <t>0; 3410</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3923</t>
+          <t>0; 4727</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2042</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5548</t>
+          <t>0; 5376</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>472; 4840</t>
+          <t>474; 4604</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1630</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 10785</t>
+          <t>0; 10030</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1565</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2674</t>
+          <t>0; 2915</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1726</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4611</t>
+          <t>0; 5431</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2199</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3728</t>
+          <t>0; 3291</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1731</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 11210</t>
+          <t>0; 10794</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 1895</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>477; 4074</t>
+          <t>478; 4109</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5028</t>
+          <t>0; 5317</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4445</t>
+          <t>0; 6057</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1622</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1368; 7749</t>
+          <t>1303; 8088</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4851</t>
+          <t>0; 5845</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2081</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6511</t>
+          <t>0; 6240</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3716</t>
+          <t>0; 3540</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 6628</t>
+          <t>0; 7209</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5235</t>
+          <t>0; 4467</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 6149</t>
+          <t>0; 6858</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2266; 9697</t>
+          <t>2055; 9743</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1694</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1965</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4621</t>
+          <t>0; 4589</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>378; 4099</t>
+          <t>396; 4456</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2044</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6499</t>
+          <t>0; 6363</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6160</t>
+          <t>0; 6283</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1917; 7689</t>
+          <t>2100; 8262</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 1969</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 6316</t>
+          <t>0; 7225</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 7521</t>
+          <t>0; 6779</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2915; 9990</t>
+          <t>3047; 10045</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 705</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2145</t>
+          <t>0; 1641</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>725; 7391</t>
+          <t>728; 7256</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2079</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1171; 9763</t>
+          <t>1171; 9800</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2702; 10371</t>
+          <t>2745; 10848</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>731; 7003</t>
+          <t>732; 7271</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 2079</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1171; 9763</t>
+          <t>1171; 9800</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3233; 11651</t>
+          <t>2882; 10782</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 6085</t>
+          <t>0; 6390</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1056; 14792</t>
+          <t>1039; 14098</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4488</t>
+          <t>0; 6211</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4228; 12598</t>
+          <t>4126; 12946</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2104; 11637</t>
+          <t>2066; 11894</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>983; 8606</t>
+          <t>986; 8630</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2480; 15345</t>
+          <t>2419; 15482</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>10377; 21782</t>
+          <t>9407; 21399</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3620; 14944</t>
+          <t>3573; 13827</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3182; 17320</t>
+          <t>3190; 17124</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3608; 16420</t>
+          <t>3305; 15999</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15821; 30334</t>
+          <t>16473; 30776</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$amigo-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P55$amigo-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,28</t>
+          <t>0,0; 36,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,28</t>
+          <t>0,0; 56,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,35</t>
+          <t>0,0; 20,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,12</t>
+          <t>0,0; 29,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -752,17 +752,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 29,83</t>
+          <t>3,1; 29,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,08</t>
+          <t>0,0; 23,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,93</t>
+          <t>0,0; 44,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 19,23</t>
+          <t>1,91; 18,99</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,47</t>
+          <t>0,0; 18,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,94</t>
+          <t>0,0; 76,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,17 +887,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,14</t>
+          <t>0,0; 68,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,86</t>
+          <t>0,0; 25,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,27</t>
+          <t>0,0; 30,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,78</t>
+          <t>0,0; 30,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 14,77</t>
+          <t>1,49; 15,42</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,05</t>
+          <t>0,0; 43,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,76</t>
+          <t>0,0; 11,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,58</t>
+          <t>0,0; 28,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,54</t>
+          <t>0,0; 14,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,85</t>
+          <t>0,0; 24,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 9,7</t>
+          <t>0,99; 9,12</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>0,0; 7,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,93</t>
+          <t>0,0; 7,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 11,23</t>
+          <t>1,74; 10,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,95</t>
+          <t>0,0; 24,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,32 +1167,32 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,01</t>
+          <t>0,0; 20,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,13</t>
+          <t>0,0; 10,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,67</t>
+          <t>0,0; 7,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,04</t>
+          <t>0,0; 7,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,43</t>
+          <t>0,0; 8,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 8,79</t>
+          <t>1,92; 8,53</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,7</t>
+          <t>0,0; 9,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 14,82</t>
+          <t>1,23; 14,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,62</t>
+          <t>0,0; 7,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,85</t>
+          <t>0,0; 11,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 8,87</t>
+          <t>2,3; 8,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,24 +1322,24 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,04</t>
+          <t>0,0; 6,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,76</t>
+          <t>0,0; 8,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 8,15</t>
+          <t>2,47; 7,85</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,51</t>
+          <t>0,0; 75,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,04</t>
+          <t>0,5; 4,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,65</t>
+          <t>0,81; 7,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,69</t>
+          <t>2,06; 8,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,02</t>
+          <t>0,51; 4,97</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,65</t>
+          <t>0,81; 7,37</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,01; 7,53</t>
+          <t>2,16; 8,93</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,05</t>
+          <t>0,0; 4,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 9,64</t>
+          <t>0,71; 9,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,11</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 8,36</t>
+          <t>2,44; 7,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,15</t>
+          <t>0,91; 5,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,1</t>
+          <t>0,36; 3,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,86</t>
+          <t>1,33; 6,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,92; 6,65</t>
+          <t>3,14; 6,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,87</t>
+          <t>0,91; 3,99</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,03</t>
+          <t>0,74; 4,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,15</t>
+          <t>0,89; 4,16</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,46</t>
+          <t>3,3; 6,31</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>502</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2249</t>
         </is>
       </c>
     </row>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3883</t>
+          <t>0; 3702</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4812</t>
+          <t>0; 4782</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2921</t>
+          <t>0; 2574</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4828</t>
+          <t>0; 4001</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1962,17 +1962,17 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>432; 4134</t>
+          <t>465; 4488</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5895</t>
+          <t>0; 5491</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4656</t>
+          <t>0; 5176</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>525; 4973</t>
+          <t>525; 5221</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>688</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>1793</t>
         </is>
       </c>
     </row>
@@ -2150,12 +2150,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4621</t>
+          <t>0; 3527</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4064</t>
+          <t>0; 4075</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2165,17 +2165,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4841</t>
+          <t>0; 4593</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3410</t>
+          <t>0; 3938</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4727</t>
+          <t>0; 4969</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5376</t>
+          <t>0; 5256</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>474; 4604</t>
+          <t>510; 5287</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>507</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>974</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1480</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 10030</t>
+          <t>0; 10727</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2915</t>
+          <t>0; 2553</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5431</t>
+          <t>0; 5362</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3291</t>
+          <t>0; 3400</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 10794</t>
+          <t>0; 10555</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>478; 4109</t>
+          <t>464; 4256</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4985</t>
         </is>
       </c>
     </row>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5317</t>
+          <t>0; 5039</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6057</t>
+          <t>0; 5417</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1303; 8088</t>
+          <t>1343; 7938</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5845</t>
+          <t>0; 5853</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2581,32 +2581,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6240</t>
+          <t>0; 6629</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3540</t>
+          <t>0; 4382</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 7209</t>
+          <t>0; 6654</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 4467</t>
+          <t>0; 6507</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 6858</t>
+          <t>0; 6266</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2055; 9743</t>
+          <t>2289; 10143</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>6516</t>
         </is>
       </c>
     </row>
@@ -2769,12 +2769,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4589</t>
+          <t>0; 4726</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>396; 4456</t>
+          <t>406; 4737</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2784,17 +2784,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6363</t>
+          <t>0; 6439</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6283</t>
+          <t>0; 5951</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2100; 8262</t>
+          <t>2321; 8981</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2804,24 +2804,24 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 7225</t>
+          <t>0; 7325</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 6779</t>
+          <t>0; 8682</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3047; 10045</t>
+          <t>3296; 10484</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>516</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6061</t>
+          <t>6792</t>
         </is>
       </c>
     </row>
@@ -2982,12 +2982,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 1641</t>
+          <t>0; 1660</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>728; 7256</t>
+          <t>725; 7031</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2997,17 +2997,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1171; 9800</t>
+          <t>1187; 10850</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2745; 10848</t>
+          <t>3131; 13385</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>732; 7271</t>
+          <t>734; 7207</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1171; 9800</t>
+          <t>1187; 10850</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2882; 10782</t>
+          <t>3335; 13777</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>14823</t>
+          <t>16255</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>22374</t>
+          <t>23816</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 6390</t>
+          <t>0; 5643</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1039; 14098</t>
+          <t>1040; 13502</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 6211</t>
+          <t>0; 4106</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4126; 12946</t>
+          <t>4063; 12916</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2066; 11894</t>
+          <t>2095; 11614</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>986; 8630</t>
+          <t>992; 8682</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2419; 15482</t>
+          <t>3522; 15932</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9407; 21399</t>
+          <t>10969; 24259</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573; 13827</t>
+          <t>3256; 14253</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3190; 17124</t>
+          <t>3136; 17431</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3305; 15999</t>
+          <t>3431; 16030</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>16473; 30776</t>
+          <t>17025; 32528</t>
         </is>
       </c>
     </row>
